--- a/resources/ERP_Sheets_Extracted/ERP Sheets/Sustainability Metrics Sheet.xlsx
+++ b/resources/ERP_Sheets_Extracted/ERP Sheets/Sustainability Metrics Sheet.xlsx
@@ -1,148 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\ERP For Startup\ERP\ERP\ERP Sheets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{765F1322-CEDB-4167-9123-E9E25D61F2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1836FBD7-3C65-4D61-9336-D78C609596E2}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
-  <si>
-    <t>Sr No</t>
-  </si>
-  <si>
-    <t>Columns</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Report</t>
-  </si>
-  <si>
-    <t>Validation</t>
-  </si>
-  <si>
-    <t>Prototype</t>
-  </si>
-  <si>
-    <t>What was actually delivered</t>
-  </si>
-  <si>
-    <t>Reference ID</t>
-  </si>
-  <si>
-    <t>SWA-2025-PRJ-068</t>
-  </si>
-  <si>
-    <t>Compliant with Green Standards</t>
-  </si>
-  <si>
-    <t>SWA-2025-PRJ-065</t>
-  </si>
-  <si>
-    <t>SWA-2025-PRJ-066</t>
-  </si>
-  <si>
-    <t>SWA-2025-PRJ-067</t>
-  </si>
-  <si>
-    <t>SWA-2025-PRJ-069</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>IGBC, LEED</t>
-  </si>
-  <si>
-    <t>GRIHA</t>
-  </si>
-  <si>
-    <t>SDG</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Total Energy Saved (kWh)</t>
-  </si>
-  <si>
-    <t>CO2 emissions avoided (tCO2e)</t>
-  </si>
-  <si>
-    <t>Lifecycle Cost savings delivered (INR)</t>
-  </si>
-  <si>
-    <t>Payback Period (Months)</t>
-  </si>
-  <si>
-    <t>Insulation Efficiency (Actual / Expected)</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -160,25 +61,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -498,161 +459,284 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0850EC78-94D7-43A3-872C-866B80F6FEC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:V7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" customWidth="1"/>
-    <col min="7" max="7" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.36328125" customWidth="1"/>
-    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.1796875" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="17" width="17.36328125" customWidth="1"/>
-    <col min="18" max="18" width="23.54296875" customWidth="1"/>
-    <col min="19" max="19" width="24.81640625" customWidth="1"/>
-    <col min="20" max="20" width="16.90625" customWidth="1"/>
-    <col min="21" max="21" width="20.81640625" customWidth="1"/>
+    <col width="12.453125" customWidth="1" min="3" max="3"/>
+    <col width="17.6328125" customWidth="1" min="4" max="4"/>
+    <col width="15" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="13.1796875" customWidth="1" min="6" max="6"/>
+    <col width="14.6328125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="19.1796875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="17.90625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12.36328125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="13.36328125" customWidth="1" min="12" max="12"/>
+    <col width="18.36328125" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="19.1796875" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="17.36328125" customWidth="1" min="17" max="17"/>
+    <col width="23.54296875" customWidth="1" min="18" max="18"/>
+    <col width="24.81640625" customWidth="1" min="19" max="19"/>
+    <col width="16.90625" customWidth="1" min="20" max="20"/>
+    <col width="20.81640625" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="43.5" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Columns</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Sr No</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Reference ID</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Compliant with Green Standards</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Total Energy Saved (kWh)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>CO2 emissions avoided (tCO2e)</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Lifecycle Cost savings delivered (INR)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Efficiency (Actual / Expected)</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Payback Period (Months)</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="n"/>
+      <c r="T2" s="1" t="n"/>
+      <c r="U2" s="1" t="n"/>
+      <c r="V2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SWA-2025-PRJ-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SWA-2025-DBR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Green certified</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SWA-2025-PRJ-002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SWA-2025-DBR-002</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LEED target</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SWA-2025-PRJ-003</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SWA-2025-CAS-001</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
+      <c r="F5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B3">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SWA-2025-PRJ-001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SWA-2025-GAD-001</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>0.89</v>
-      </c>
-      <c r="T3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="F6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Net zero target</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SWA-2025-PRJ-002</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4">
-        <v>0.91</v>
-      </c>
-      <c r="T4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>0.84</v>
-      </c>
-      <c r="T6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" t="s">
-        <v>24</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>